--- a/bindings/excel/examples/workbooks/portfolio_aggregation_example.xlsx
+++ b/bindings/excel/examples/workbooks/portfolio_aggregation_example.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6018bc907cdb526/Escritorio/Pega/quantsupport/bindings/excel/examples/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_6763025740B1A133E0263D5BDED076BB3B50E021" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4DD542A-03DA-4588-87D3-3690468D49E0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -23,7 +17,6 @@
     <sheet name="7 Risk" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Start Here'!$A$1:$F$30</definedName>
     <definedName name="Portfolio_Book">'3 Build'!$B$79</definedName>
     <definedName name="Portfolio_C01_Index">'1 Positions'!$F$17</definedName>
     <definedName name="Portfolio_C01_Instrument">'3 Build'!$B$16</definedName>
@@ -120,6 +113,7 @@
     <definedName name="Portfolio_SwapMaturity">'1 Positions'!$B$10</definedName>
     <definedName name="Portfolio_TermRates">'2 Market'!$C$7:$C$9</definedName>
     <definedName name="Portfolio_ValuationDate">'1 Positions'!$B$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Start Here'!$A$1:$F$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1 Positions'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2 Market'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'3 Build'!$1:$6</definedName>
@@ -128,30 +122,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'6 Cashflows'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'7 Risk'!$1:$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -164,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -203,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -221,12 +202,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -239,7 +220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -252,7 +233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,12 +251,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -288,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -301,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -314,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -340,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="B22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -353,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -366,7 +347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="B28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -379,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="B31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -392,7 +373,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+    <comment ref="B34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -405,7 +386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
+    <comment ref="B37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -418,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B40" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
+    <comment ref="B40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -431,7 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B43" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
+    <comment ref="B43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -444,7 +425,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
+    <comment ref="B46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -457,7 +438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
+    <comment ref="B49" authorId="0">
       <text>
         <r>
           <rPr>
@@ -470,7 +451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
+    <comment ref="B52" authorId="0">
       <text>
         <r>
           <rPr>
@@ -483,7 +464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
+    <comment ref="B55" authorId="0">
       <text>
         <r>
           <rPr>
@@ -496,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
+    <comment ref="B58" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
+    <comment ref="B61" authorId="0">
       <text>
         <r>
           <rPr>
@@ -522,7 +503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
+    <comment ref="B64" authorId="0">
       <text>
         <r>
           <rPr>
@@ -535,7 +516,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
+    <comment ref="B67" authorId="0">
       <text>
         <r>
           <rPr>
@@ -548,7 +529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
+    <comment ref="B79" authorId="0">
       <text>
         <r>
           <rPr>
@@ -561,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B82" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
+    <comment ref="B82" authorId="0">
       <text>
         <r>
           <rPr>
@@ -579,12 +560,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -597,7 +578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -610,7 +591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -623,7 +604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -636,7 +617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1185,12 +1166,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="165" formatCode="0.0000%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00)"/>
+    <numFmt numFmtId="167" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1364,9 +1347,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1384,53 +1373,26 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1438,132 +1400,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/volatileDependencies.xml><?xml version="1.0" encoding="utf-8"?>
-<volTypes xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <volType type="realTimeData">
-    <main first="rtdsrv_679dc4253c1b45d99cc5011b9a1dfcee">
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>182b9daf-6661-435b-816f-7d4c149a4623</stp>
-        <tr r="B31" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>a682793d-d4f5-4b04-9ba6-55557b81a143</stp>
-        <tr r="B22" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>288413de-c479-4e58-a694-0027e31bb8e5</stp>
-        <tr r="B58" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>05efaa17-6faa-46cd-b61a-8accf17bc48d</stp>
-        <tr r="A7" s="6"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>f1b2528d-c7bc-4371-a00f-bbbf7629be8f</stp>
-        <tr r="B26" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>8b38cbef-9e02-47bd-81bc-cf42175bb96a</stp>
-        <tr r="B49" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>d250d04b-c795-480d-898c-58d3736d6bfc</stp>
-        <tr r="B40" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>8e7111cd-2906-4635-a44a-276feacffd14</stp>
-        <tr r="B7" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>21af692a-8f08-4c16-a680-bfd0f65f4d15</stp>
-        <tr r="A7" s="7"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>0b5f4d23-f0ec-4e9e-bf04-9803961531e1</stp>
-        <tr r="B25" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>492a7d1b-7ce1-4497-9403-1bd840e22795</stp>
-        <tr r="B23" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>5806ae1e-f62c-480d-a63d-2d90ca903aba</stp>
-        <tr r="B67" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>4d54c061-95c8-41de-b147-3251cd8eeeb6</stp>
-        <tr r="B21" s="5"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>79f41826-5f0c-4dba-90d1-c20abee12d29</stp>
-        <tr r="B82" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>c762898b-f674-4911-bbb7-ab8c0bb39808</stp>
-        <tr r="B22" s="4"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>eac68346-16b9-4fcd-94ef-4edc768c7175</stp>
-        <tr r="A7" s="8"/>
-      </tp>
-      <tp>
-        <v>3</v>
-        <stp/>
-        <stp>4361867c-b2c0-4003-8818-027865399b44</stp>
-        <tr r="B24" s="5"/>
-      </tp>
-    </main>
-  </volType>
-</volTypes>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1601,7 +1444,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1635,7 +1478,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1670,10 +1512,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1846,12 +1687,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="26.1" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="26.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -1860,271 +1701,271 @@
     <col min="6" max="6" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-    </row>
-    <row r="6" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="6" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="9" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-    </row>
-    <row r="10" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="12" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="19" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="19" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1">
+      <c r="A20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="12" t="s">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
+      <c r="A21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="12" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1">
+      <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="12" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="24" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="24" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A24" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="29" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="29" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" ht="26.25" customHeight="1">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -2151,22 +1992,22 @@
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A29:F30"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A29:F30"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B10" location="'1 Positions'!A1" display="1 Positions" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B11" location="'2 Market'!A1" display="2 Market" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B12" location="'3 Build'!A1" display="3 Build" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B13" location="'4 Results'!A1" display="4 Results" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B14" location="'5 Coupons'!A1" display="5 Coupons" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B15" location="'6 Cashflows'!A1" display="6 Cashflows" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B16" location="'7 Risk'!A1" display="7 Risk" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B10" location="'1 Positions'!A1" display="1 Positions"/>
+    <hyperlink ref="B11" location="'2 Market'!A1" display="2 Market"/>
+    <hyperlink ref="B12" location="'3 Build'!A1" display="3 Build"/>
+    <hyperlink ref="B13" location="'4 Results'!A1" display="4 Results"/>
+    <hyperlink ref="B14" location="'5 Coupons'!A1" display="5 Coupons"/>
+    <hyperlink ref="B15" location="'6 Cashflows'!A1" display="6 Cashflows"/>
+    <hyperlink ref="B16" location="'7 Risk'!A1" display="7 Risk"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2174,13 +2015,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
@@ -2191,396 +2032,428 @@
     <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-    </row>
-    <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:8" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" ht="32.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="32.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="32.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="32.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="32.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:8" ht="36" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="24" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>100000</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="12">
         <v>0.04</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="1" t="str">
+      <c r="H17" s="1">
         <f>Portfolio_DepositMaturity</f>
-        <v>2026-09-02</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="24" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>300000</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="12">
         <v>0.06</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="1"/>
+      <c r="F18" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="1" t="str">
+      <c r="H18" s="1">
         <f>Portfolio_DepositMaturity</f>
-        <v>2026-09-02</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="24" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>100000</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="12">
         <v>0.04</v>
       </c>
-      <c r="E19" s="9">
-        <v>1E-3</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="E19" s="12">
+        <v>0.001</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H19" s="1" t="str">
+      <c r="H19" s="1">
         <f>Portfolio_SwapMaturity</f>
-        <v>2028-03-02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="24" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <v>300000</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="12">
         <v>0.06</v>
       </c>
-      <c r="E20" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="E20" s="12">
+        <v>0.003</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H20" s="1" t="str">
+      <c r="H20" s="1">
         <f>Portfolio_SwapMaturity</f>
-        <v>2028-03-02</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="24" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <v>200000</v>
       </c>
-      <c r="D21" s="9">
-        <v>5.5E-2</v>
-      </c>
-      <c r="E21" s="9">
-        <v>2E-3</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="D21" s="12">
+        <v>0.055</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.002</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="1" t="str">
+      <c r="H21" s="1">
         <f>Portfolio_SwapMaturity</f>
-        <v>2028-03-02</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <v>50000</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="12">
         <v>0.04</v>
       </c>
-      <c r="E22" s="9">
-        <v>1E-3</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="E22" s="12">
+        <v>0.001</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="1" t="str">
+      <c r="H22" s="1">
         <f>Portfolio_SwapMaturity</f>
-        <v>2028-03-02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="24" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-    </row>
-    <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-    </row>
-    <row r="27" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="24" customHeight="1">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="36" customHeight="1">
+      <c r="A27" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" ht="24" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="24" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-    </row>
-    <row r="30" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="24" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C30:H30"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H3"/>
     <mergeCell ref="A24:H25"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
+    <mergeCell ref="C30:H30"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17:G22" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G17">
       <formula1>"Receive,Pay"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C22" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G18">
+      <formula1>"Receive,Pay"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G19">
+      <formula1>"Receive,Pay"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G20">
+      <formula1>"Receive,Pay"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21">
+      <formula1>"Receive,Pay"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C21">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22">
+      <formula1>"Receive,Pay"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="H4" location="'2 Market'!A1" display="Next → 2 Market" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="H4" location="'2 Market'!A1" display="Next → 2 Market"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -2592,160 +2465,160 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF337AB7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="40.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="58.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="24" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="12">
         <v>0.03</v>
       </c>
-      <c r="C7" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="12">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="24" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="12">
         <v>0.03</v>
       </c>
-      <c r="C8" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="12">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="24" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="12">
         <v>0.03</v>
       </c>
-      <c r="C9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="C9" s="12">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="36" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="7" t="str" cm="1">
+      <c r="B13" s="10" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.CONTEXT.CREATE("Portfolio.Root",Portfolio_ValuationDate,Portfolio_Currency,"SOFR")</f>
-        <v>QSObject:PricingContext:w1~Portfolio.Root:1</v>
-      </c>
-      <c r="C13" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
-        <v>=QS.CONTEXT.CREATE("Portfolio.Root";Portfolio_ValuationDate;Portfolio_Currency;"SOFR")</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-    </row>
-    <row r="16" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A14" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
+        <v>=QS.CONTEXT.CREATE("Portfolio.Root", Portfolio_ValuationDate, Portfolio_Currency, "SOFR")</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="7" t="str" cm="1">
+      <c r="B16" s="10" cm="1" t="str">
         <f t="array" ref="B16">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Portfolio_Root,"SOFR",Portfolio_Pillars,Portfolio_SofrRates,"Actual360","Continuous","Annual","Linear",TRUE)</f>
-        <v>QSObject:ContextInput:w1~context.input.20415403f72e339c.3170917791056.15.1:3</v>
-      </c>
-      <c r="C16" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Portfolio_Root;"SOFR";Portfolio_Pillars;Portfolio_SofrRates;"Actual360";"Continuous";"Annual";"Linear";VERDADERO)</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-    </row>
-    <row r="19" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="17" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A17" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Portfolio_Root, "SOFR", Portfolio_Pillars, Portfolio_SofrRates, "Actual360", "Continuous", "Annual", "Linear", TRUE)</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+    </row>
+    <row r="19" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B19" s="7" t="str" cm="1">
+      <c r="B19" s="10" cm="1" t="str">
         <f t="array" ref="B19">_xll.QS.CONTEXT.ADD.ZERO.CURVE(Portfolio_Root,"TermSOFR3m",Portfolio_Pillars,Portfolio_TermRates,"Actual360","Continuous","Annual","Linear",TRUE)</f>
-        <v>QSObject:ContextInput:w1~context.input.a43b9aaeef0d8d90.3170917791056.18.1:2</v>
-      </c>
-      <c r="C19" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Portfolio_Root;"TermSOFR3m";Portfolio_Pillars;Portfolio_TermRates;"Actual360";"Continuous";"Annual";"Linear";VERDADERO)</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A20" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
+        <v>=QS.CONTEXT.ADD.ZERO.CURVE(Portfolio_Root, "TermSOFR3m", Portfolio_Pillars, Portfolio_TermRates, "Actual360", "Continuous", "Annual", "Linear", TRUE)</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2756,8 +2629,8 @@
     <mergeCell ref="A20:C20"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="C4" location="'3 Build'!A1" display="Next → 3 Build" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'3 Build'!A1" display="Next → 3 Build"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -2769,604 +2642,604 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.7109375" style="1" customWidth="1"/>
     <col min="2" max="3" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">Portfolio_Root</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="10">
+        <f>Portfolio_Root</f>
+        <v/>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
-        <v>=QS.CONTEXT.PREPARE("Portfolio.Context";Portfolio_Root;Portfolio_MarketInputs)</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-    </row>
-    <row r="10" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="8" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A8" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B7),",",", ")</f>
+        <v>=Portfolio_Root</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+    </row>
+    <row r="10" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="7" t="str" cm="1">
+      <c r="B10" s="10" cm="1" t="str">
         <f t="array" ref="B10">_xll.QS.DISCOUNT.POLICY.CSA("Portfolio.Policy",Portfolio_Currency,"SOFR")</f>
-        <v>QSObject:SingleCurveCSADiscountPolicy:w1~Portfolio.Policy:5</v>
-      </c>
-      <c r="C10" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
-        <v>=QS.DISCOUNT.POLICY.CSA("Portfolio.Policy";Portfolio_Currency;"SOFR")</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-    </row>
-    <row r="13" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A11" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B10),",",", ")</f>
+        <v>=QS.DISCOUNT.POLICY.CSA("Portfolio.Policy", Portfolio_Currency, "SOFR")</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+    </row>
+    <row r="13" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A13" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="7" t="str" cm="1">
+      <c r="B13" s="10" cm="1" t="str">
         <f t="array" ref="B13">_xll.QS.PRICER.CREATE("Portfolio.Pricer","DiscountedCashflowPricer",Portfolio_Policy)</f>
-        <v>QSObject:Pricer:w1~Portfolio.Pricer:7</v>
-      </c>
-      <c r="C13" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
-        <v>=QS.PRICER.CREATE("Portfolio.Pricer";"DiscountedCashflowPricer";Portfolio_Policy)</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-    </row>
-    <row r="16" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="14" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A14" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B13),",",", ")</f>
+        <v>=QS.PRICER.CREATE("Portfolio.Pricer", "DiscountedCashflowPricer", Portfolio_Policy)</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="16" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="7" t="str" cm="1">
-        <f t="array" ref="B16">_xll.QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C01.Instrument",Portfolio_Start,Portfolio_C01_Maturity,Portfolio_Currency,Portfolio_C01_Index,Portfolio_C01_Notional,Portfolio_C01_Rate,"Actual360","Simple","Annual")</f>
-        <v>QSObject:FixedRateDeposit:w1~Portfolio.C01.Instrument:14</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="10" cm="1" t="str">
+        <f t="array" ref="B16">_xll.QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C01.Instrument",Portfolio_Context,Portfolio_Start,Portfolio_C01_Maturity,Portfolio_Currency,Portfolio_C01_Index,Portfolio_C01_Notional,Portfolio_C01_Rate,"Actual360","Simple","Annual")</f>
+        <v/>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
-        <v>=QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C01.Instrument";Portfolio_Start;Portfolio_C01_Maturity;Portfolio_Currency;Portfolio_C01_Index;Portfolio_C01_Notional;Portfolio_C01_Rate;"Actual360";"Simple";"Annual")</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-    </row>
-    <row r="19" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="17" spans="1:3" ht="48" customHeight="1">
+      <c r="A17" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B16),",",", ")</f>
+        <v>=QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C01.Instrument", Portfolio_Context, Portfolio_Start, Portfolio_C01_Maturity, Portfolio_Currency, Portfolio_C01_Index, Portfolio_C01_Notional, Portfolio_C01_Rate, "Actual360", "Simple", "Annual")</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+    </row>
+    <row r="19" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A19" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B19" s="7" t="str" cm="1">
-        <f t="array" ref="B19">_xll.QS.TRADE.CREATE("Portfolio.C01.Trade",Portfolio_C01_Instrument,Portfolio_ValuationDate,Portfolio_C01_Side)</f>
-        <v>QSObject:FixedRateDepositTrade:w1~Portfolio.C01.Trade:16</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="10" cm="1" t="str">
+        <f t="array" ref="B19">_xll.QS.TRADE.CREATE("Portfolio.C01.Trade",Portfolio_Context,Portfolio_C01_Instrument,Portfolio_ValuationDate,Portfolio_C01_Side)</f>
+        <v/>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Portfolio.C01.Trade";Portfolio_C01_Instrument;Portfolio_ValuationDate;Portfolio_C01_Side)</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-    </row>
-    <row r="22" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="20" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A20" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B19),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Portfolio.C01.Trade", Portfolio_Context, Portfolio_C01_Instrument, Portfolio_ValuationDate, Portfolio_C01_Side)</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+    </row>
+    <row r="22" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C01_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="10" cm="1" t="str">
+        <f t="array" ref="B22">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C01_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
+        <v/>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(Portfolio_Context;Portfolio_C01_Trade;Portfolio_Requests;;Portfolio_Pricer)</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-    </row>
-    <row r="25" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="23" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A23" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B22),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(Portfolio_Context, Portfolio_C01_Trade, Portfolio_Requests, Portfolio_Pricer)</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+    </row>
+    <row r="25" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B25" s="7" t="str" cm="1">
-        <f t="array" ref="B25">_xll.QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C02.Instrument",Portfolio_Start,Portfolio_C02_Maturity,Portfolio_Currency,Portfolio_C02_Index,Portfolio_C02_Notional,Portfolio_C02_Rate,"Actual360","Simple","Annual")</f>
-        <v>QSObject:FixedRateDeposit:w1~Portfolio.C02.Instrument:15</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="10" cm="1" t="str">
+        <f t="array" ref="B25">_xll.QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C02.Instrument",Portfolio_Context,Portfolio_Start,Portfolio_C02_Maturity,Portfolio_Currency,Portfolio_C02_Index,Portfolio_C02_Notional,Portfolio_C02_Rate,"Actual360","Simple","Annual")</f>
+        <v/>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
-        <v>=QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C02.Instrument";Portfolio_Start;Portfolio_C02_Maturity;Portfolio_Currency;Portfolio_C02_Index;Portfolio_C02_Notional;Portfolio_C02_Rate;"Actual360";"Simple";"Annual")</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-    </row>
-    <row r="28" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="26" spans="1:3" ht="48" customHeight="1">
+      <c r="A26" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B25),",",", ")</f>
+        <v>=QS.INSTRUMENT.FIXED.RATE.DEPOSIT("Portfolio.C02.Instrument", Portfolio_Context, Portfolio_Start, Portfolio_C02_Maturity, Portfolio_Currency, Portfolio_C02_Index, Portfolio_C02_Notional, Portfolio_C02_Rate, "Actual360", "Simple", "Annual")</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+    </row>
+    <row r="28" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A28" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="7" t="str" cm="1">
-        <f t="array" ref="B28">_xll.QS.TRADE.CREATE("Portfolio.C02.Trade",Portfolio_C02_Instrument,Portfolio_ValuationDate,Portfolio_C02_Side)</f>
-        <v>QSObject:FixedRateDepositTrade:w1~Portfolio.C02.Trade:17</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="10" cm="1" t="str">
+        <f t="array" ref="B28">_xll.QS.TRADE.CREATE("Portfolio.C02.Trade",Portfolio_Context,Portfolio_C02_Instrument,Portfolio_ValuationDate,Portfolio_C02_Side)</f>
+        <v/>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Portfolio.C02.Trade";Portfolio_C02_Instrument;Portfolio_ValuationDate;Portfolio_C02_Side)</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-    </row>
-    <row r="31" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+    <row r="29" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A29" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B28),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Portfolio.C02.Trade", Portfolio_Context, Portfolio_C02_Instrument, Portfolio_ValuationDate, Portfolio_C02_Side)</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+    </row>
+    <row r="31" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A31" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B31" ca="1">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C02_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="B31" s="10" cm="1" t="str">
+        <f t="array" ref="B31">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C02_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
+        <v/>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(Portfolio_Context;Portfolio_C02_Trade;Portfolio_Requests;;Portfolio_Pricer)</v>
-      </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-    </row>
-    <row r="34" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="32" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A32" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B31),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(Portfolio_Context, Portfolio_C02_Trade, Portfolio_Requests, Portfolio_Pricer)</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+    </row>
+    <row r="34" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A34" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="7" t="str" cm="1">
-        <f t="array" ref="B34">_xll.QS.INSTRUMENT.SWAP("Portfolio.C03.Instrument",Portfolio_Start,Portfolio_C03_Maturity,Portfolio_Currency,Portfolio_C03_Index,Portfolio_C03_Notional,Portfolio_C03_Rate,Portfolio_C03_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
-        <v>QSObject:Swap:w1~Portfolio.C03.Instrument:9</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="B34" s="10" cm="1" t="str">
+        <f t="array" ref="B34">_xll.QS.INSTRUMENT.SWAP("Portfolio.C03.Instrument",Portfolio_Context,Portfolio_Start,Portfolio_C03_Maturity,Portfolio_Currency,Portfolio_C03_Index,Portfolio_C03_Notional,Portfolio_C03_Rate,Portfolio_C03_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
+        <v/>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
-        <v>=QS.INSTRUMENT.SWAP("Portfolio.C03.Instrument";Portfolio_Start;Portfolio_C03_Maturity;Portfolio_Currency;Portfolio_C03_Index;Portfolio_C03_Notional;Portfolio_C03_Rate;Portfolio_C03_Spread;"Actual360";"Simple";"Annual";"Annual";"Annual")</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-    </row>
-    <row r="37" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="35" spans="1:3" ht="48" customHeight="1">
+      <c r="A35" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B34),",",", ")</f>
+        <v>=QS.INSTRUMENT.SWAP("Portfolio.C03.Instrument", Portfolio_Context, Portfolio_Start, Portfolio_C03_Maturity, Portfolio_Currency, Portfolio_C03_Index, Portfolio_C03_Notional, Portfolio_C03_Rate, Portfolio_C03_Spread, "Actual360", "Simple", "Annual", "Annual", "Annual")</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+    </row>
+    <row r="37" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A37" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="7" t="str" cm="1">
-        <f t="array" ref="B37">_xll.QS.TRADE.CREATE("Portfolio.C03.Trade",Portfolio_C03_Instrument,Portfolio_ValuationDate,Portfolio_C03_Side)</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C03.Trade:13</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="B37" s="10" cm="1" t="str">
+        <f t="array" ref="B37">_xll.QS.TRADE.CREATE("Portfolio.C03.Trade",Portfolio_Context,Portfolio_C03_Instrument,Portfolio_ValuationDate,Portfolio_C03_Side)</f>
+        <v/>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B37),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Portfolio.C03.Trade";Portfolio_C03_Instrument;Portfolio_ValuationDate;Portfolio_C03_Side)</v>
-      </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-    </row>
-    <row r="40" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+    <row r="38" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A38" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B37),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Portfolio.C03.Trade", Portfolio_Context, Portfolio_C03_Instrument, Portfolio_ValuationDate, Portfolio_C03_Side)</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+    </row>
+    <row r="40" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A40" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B40" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B40" ca="1">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C03_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="10" cm="1" t="str">
+        <f t="array" ref="B40">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C03_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
+        <v/>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(Portfolio_Context;Portfolio_C03_Trade;Portfolio_Requests;;Portfolio_Pricer)</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-    </row>
-    <row r="43" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+    <row r="41" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A41" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B40),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(Portfolio_Context, Portfolio_C03_Trade, Portfolio_Requests, Portfolio_Pricer)</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+    </row>
+    <row r="43" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A43" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="7" t="str" cm="1">
-        <f t="array" ref="B43">_xll.QS.INSTRUMENT.SWAP("Portfolio.C04.Instrument",Portfolio_Start,Portfolio_C04_Maturity,Portfolio_Currency,Portfolio_C04_Index,Portfolio_C04_Notional,Portfolio_C04_Rate,Portfolio_C04_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
-        <v>QSObject:Swap:w1~Portfolio.C04.Instrument:11</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="10" cm="1" t="str">
+        <f t="array" ref="B43">_xll.QS.INSTRUMENT.SWAP("Portfolio.C04.Instrument",Portfolio_Context,Portfolio_Start,Portfolio_C04_Maturity,Portfolio_Currency,Portfolio_C04_Index,Portfolio_C04_Notional,Portfolio_C04_Rate,Portfolio_C04_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
+        <v/>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
-        <v>=QS.INSTRUMENT.SWAP("Portfolio.C04.Instrument";Portfolio_Start;Portfolio_C04_Maturity;Portfolio_Currency;Portfolio_C04_Index;Portfolio_C04_Notional;Portfolio_C04_Rate;Portfolio_C04_Spread;"Actual360";"Simple";"Annual";"Annual";"Annual")</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-    </row>
-    <row r="46" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+    <row r="44" spans="1:3" ht="48" customHeight="1">
+      <c r="A44" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B43),",",", ")</f>
+        <v>=QS.INSTRUMENT.SWAP("Portfolio.C04.Instrument", Portfolio_Context, Portfolio_Start, Portfolio_C04_Maturity, Portfolio_Currency, Portfolio_C04_Index, Portfolio_C04_Notional, Portfolio_C04_Rate, Portfolio_C04_Spread, "Actual360", "Simple", "Annual", "Annual", "Annual")</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+    </row>
+    <row r="46" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A46" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="7" t="str" cm="1">
-        <f t="array" ref="B46">_xll.QS.TRADE.CREATE("Portfolio.C04.Trade",Portfolio_C04_Instrument,Portfolio_ValuationDate,Portfolio_C04_Side)</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C04.Trade:12</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="B46" s="10" cm="1" t="str">
+        <f t="array" ref="B46">_xll.QS.TRADE.CREATE("Portfolio.C04.Trade",Portfolio_Context,Portfolio_C04_Instrument,Portfolio_ValuationDate,Portfolio_C04_Side)</f>
+        <v/>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B46),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Portfolio.C04.Trade";Portfolio_C04_Instrument;Portfolio_ValuationDate;Portfolio_C04_Side)</v>
-      </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-    </row>
-    <row r="49" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+    <row r="47" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A47" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B46),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Portfolio.C04.Trade", Portfolio_Context, Portfolio_C04_Instrument, Portfolio_ValuationDate, Portfolio_C04_Side)</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+    </row>
+    <row r="49" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A49" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B49" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B49" ca="1">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C04_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="B49" s="10" cm="1" t="str">
+        <f t="array" ref="B49">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C04_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
+        <v/>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B49),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(Portfolio_Context;Portfolio_C04_Trade;Portfolio_Requests;;Portfolio_Pricer)</v>
-      </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-    </row>
-    <row r="52" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+    <row r="50" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A50" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B49),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(Portfolio_Context, Portfolio_C04_Trade, Portfolio_Requests, Portfolio_Pricer)</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+    </row>
+    <row r="52" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A52" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B52" s="7" t="str" cm="1">
-        <f t="array" ref="B52">_xll.QS.INSTRUMENT.SWAP("Portfolio.C05.Instrument",Portfolio_Start,Portfolio_C05_Maturity,Portfolio_Currency,Portfolio_C05_Index,Portfolio_C05_Notional,Portfolio_C05_Rate,Portfolio_C05_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
-        <v>QSObject:Swap:w1~Portfolio.C05.Instrument:4</v>
-      </c>
-      <c r="C52" s="5" t="s">
+      <c r="B52" s="10" cm="1" t="str">
+        <f t="array" ref="B52">_xll.QS.INSTRUMENT.SWAP("Portfolio.C05.Instrument",Portfolio_Context,Portfolio_Start,Portfolio_C05_Maturity,Portfolio_Currency,Portfolio_C05_Index,Portfolio_C05_Notional,Portfolio_C05_Rate,Portfolio_C05_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
+        <v/>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B52),",",", ")</f>
-        <v>=QS.INSTRUMENT.SWAP("Portfolio.C05.Instrument";Portfolio_Start;Portfolio_C05_Maturity;Portfolio_Currency;Portfolio_C05_Index;Portfolio_C05_Notional;Portfolio_C05_Rate;Portfolio_C05_Spread;"Actual360";"Simple";"Annual";"Annual";"Annual")</v>
-      </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-    </row>
-    <row r="55" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+    <row r="53" spans="1:3" ht="48" customHeight="1">
+      <c r="A53" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B52),",",", ")</f>
+        <v>=QS.INSTRUMENT.SWAP("Portfolio.C05.Instrument", Portfolio_Context, Portfolio_Start, Portfolio_C05_Maturity, Portfolio_Currency, Portfolio_C05_Index, Portfolio_C05_Notional, Portfolio_C05_Rate, Portfolio_C05_Spread, "Actual360", "Simple", "Annual", "Annual", "Annual")</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+    </row>
+    <row r="55" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A55" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B55" s="7" t="str" cm="1">
-        <f t="array" ref="B55">_xll.QS.TRADE.CREATE("Portfolio.C05.Trade",Portfolio_C05_Instrument,Portfolio_ValuationDate,Portfolio_C05_Side)</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C05.Trade:10</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="B55" s="10" cm="1" t="str">
+        <f t="array" ref="B55">_xll.QS.TRADE.CREATE("Portfolio.C05.Trade",Portfolio_Context,Portfolio_C05_Instrument,Portfolio_ValuationDate,Portfolio_C05_Side)</f>
+        <v/>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B55),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Portfolio.C05.Trade";Portfolio_C05_Instrument;Portfolio_ValuationDate;Portfolio_C05_Side)</v>
-      </c>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-    </row>
-    <row r="58" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+    <row r="56" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A56" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B55),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Portfolio.C05.Trade", Portfolio_Context, Portfolio_C05_Instrument, Portfolio_ValuationDate, Portfolio_C05_Side)</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+    </row>
+    <row r="58" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A58" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B58" ca="1">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C05_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="B58" s="10" cm="1" t="str">
+        <f t="array" ref="B58">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C05_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
+        <v/>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B58),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(Portfolio_Context;Portfolio_C05_Trade;Portfolio_Requests;;Portfolio_Pricer)</v>
-      </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-    </row>
-    <row r="61" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+    <row r="59" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A59" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B58),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(Portfolio_Context, Portfolio_C05_Trade, Portfolio_Requests, Portfolio_Pricer)</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+    </row>
+    <row r="61" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A61" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B61" s="7" t="str" cm="1">
-        <f t="array" ref="B61">_xll.QS.INSTRUMENT.SWAP("Portfolio.C06.Instrument",Portfolio_Start,Portfolio_C06_Maturity,Portfolio_Currency,Portfolio_C06_Index,Portfolio_C06_Notional,Portfolio_C06_Rate,Portfolio_C06_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
-        <v>QSObject:Swap:w1~Portfolio.C06.Instrument:6</v>
-      </c>
-      <c r="C61" s="5" t="s">
+      <c r="B61" s="10" cm="1" t="str">
+        <f t="array" ref="B61">_xll.QS.INSTRUMENT.SWAP("Portfolio.C06.Instrument",Portfolio_Context,Portfolio_Start,Portfolio_C06_Maturity,Portfolio_Currency,Portfolio_C06_Index,Portfolio_C06_Notional,Portfolio_C06_Rate,Portfolio_C06_Spread,"Actual360","Simple","Annual","Annual","Annual")</f>
+        <v/>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B61),",",", ")</f>
-        <v>=QS.INSTRUMENT.SWAP("Portfolio.C06.Instrument";Portfolio_Start;Portfolio_C06_Maturity;Portfolio_Currency;Portfolio_C06_Index;Portfolio_C06_Notional;Portfolio_C06_Rate;Portfolio_C06_Spread;"Actual360";"Simple";"Annual";"Annual";"Annual")</v>
-      </c>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-    </row>
-    <row r="64" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+    <row r="62" spans="1:3" ht="48" customHeight="1">
+      <c r="A62" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B61),",",", ")</f>
+        <v>=QS.INSTRUMENT.SWAP("Portfolio.C06.Instrument", Portfolio_Context, Portfolio_Start, Portfolio_C06_Maturity, Portfolio_Currency, Portfolio_C06_Index, Portfolio_C06_Notional, Portfolio_C06_Rate, Portfolio_C06_Spread, "Actual360", "Simple", "Annual", "Annual", "Annual")</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+    </row>
+    <row r="64" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A64" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="7" t="str" cm="1">
-        <f t="array" ref="B64">_xll.QS.TRADE.CREATE("Portfolio.C06.Trade",Portfolio_C06_Instrument,Portfolio_ValuationDate,Portfolio_C06_Side)</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C06.Trade:8</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="B64" s="10" cm="1" t="str">
+        <f t="array" ref="B64">_xll.QS.TRADE.CREATE("Portfolio.C06.Trade",Portfolio_Context,Portfolio_C06_Instrument,Portfolio_ValuationDate,Portfolio_C06_Side)</f>
+        <v/>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B64),",",", ")</f>
-        <v>=QS.TRADE.CREATE("Portfolio.C06.Trade";Portfolio_C06_Instrument;Portfolio_ValuationDate;Portfolio_C06_Side)</v>
-      </c>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-    </row>
-    <row r="67" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
+    <row r="65" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A65" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B64),",",", ")</f>
+        <v>=QS.TRADE.CREATE("Portfolio.C06.Trade", Portfolio_Context, Portfolio_C06_Instrument, Portfolio_ValuationDate, Portfolio_C06_Side)</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+    </row>
+    <row r="67" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A67" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B67" ca="1">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C06_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="B67" s="10" cm="1" t="str">
+        <f t="array" ref="B67">_xll.QS.EVALUATE.RESULTS(Portfolio_Context,Portfolio_C06_Trade,Portfolio_Requests,Portfolio_Pricer)</f>
+        <v/>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B67),",",", ")</f>
-        <v>=QS.EVALUATE.RESULTS(Portfolio_Context;Portfolio_C06_Trade;Portfolio_Requests;;Portfolio_Pricer)</v>
-      </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-    </row>
-    <row r="70" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+    <row r="68" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A68" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B67),",",", ")</f>
+        <v>=QS.EVALUATE.RESULTS(Portfolio_Context, Portfolio_C06_Trade, Portfolio_Requests, Portfolio_Pricer)</v>
+      </c>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+    </row>
+    <row r="70" spans="1:3" ht="36" customHeight="1">
+      <c r="A70" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="24" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="7" t="str">
+      <c r="B71" s="10">
         <f>Portfolio_C01_Trade</f>
-        <v>QSObject:FixedRateDepositTrade:w1~Portfolio.C01.Trade:16</v>
-      </c>
-      <c r="C71" s="7" t="e">
-        <f ca="1">Portfolio_C01_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="C71" s="10">
+        <f>Portfolio_C01_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="24" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="7" t="str">
+      <c r="B72" s="10">
         <f>Portfolio_C02_Trade</f>
-        <v>QSObject:FixedRateDepositTrade:w1~Portfolio.C02.Trade:17</v>
-      </c>
-      <c r="C72" s="7" t="e">
-        <f ca="1">Portfolio_C02_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="C72" s="10">
+        <f>Portfolio_C02_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="24" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="7" t="str">
+      <c r="B73" s="10">
         <f>Portfolio_C03_Trade</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C03.Trade:13</v>
-      </c>
-      <c r="C73" s="7" t="e">
-        <f ca="1">Portfolio_C03_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="C73" s="10">
+        <f>Portfolio_C03_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="24" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="7" t="str">
+      <c r="B74" s="10">
         <f>Portfolio_C04_Trade</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C04.Trade:12</v>
-      </c>
-      <c r="C74" s="7" t="e">
-        <f ca="1">Portfolio_C04_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="C74" s="10">
+        <f>Portfolio_C04_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="24" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B75" s="7" t="str">
+      <c r="B75" s="10">
         <f>Portfolio_C05_Trade</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C05.Trade:10</v>
-      </c>
-      <c r="C75" s="7" t="e">
-        <f ca="1">Portfolio_C05_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="C75" s="10">
+        <f>Portfolio_C05_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="24" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B76" s="7" t="str">
+      <c r="B76" s="10">
         <f>Portfolio_C06_Trade</f>
-        <v>QSObject:SwapTrade:w1~Portfolio.C06.Trade:8</v>
-      </c>
-      <c r="C76" s="7" t="e">
-        <f ca="1">Portfolio_C06_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
+        <v/>
+      </c>
+      <c r="C76" s="10">
+        <f>Portfolio_C06_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A79" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B79" s="7" t="str" cm="1">
+      <c r="B79" s="10" cm="1" t="str">
         <f t="array" ref="B79">_xll.QS.PORTFOLIO.CREATE("Portfolio.Book",Portfolio_Members)</f>
-        <v>QSObject:Portfolio:w1~Portfolio.Book:18</v>
-      </c>
-      <c r="C79" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B79),",",", ")</f>
-        <v>=QS.PORTFOLIO.CREATE("Portfolio.Book";Portfolio_Members)</v>
-      </c>
-      <c r="B80" s="22"/>
-      <c r="C80" s="22"/>
-    </row>
-    <row r="82" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+    <row r="80" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A80" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B79),",",", ")</f>
+        <v>=QS.PORTFOLIO.CREATE("Portfolio.Book", Portfolio_Members)</v>
+      </c>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13"/>
+    </row>
+    <row r="82" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A82" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B82" s="7" t="e" cm="1">
-        <f t="array" aca="1" ref="B82" ca="1">_xll.QS.EVALUATE.PORTFOLIO(Portfolio_Context,Portfolio_Book,Portfolio_Pricer,Portfolio_Requests,Portfolio_Currency)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C82" s="5" t="s">
+      <c r="B82" s="10" cm="1" t="str">
+        <f t="array" ref="B82">_xll.QS.EVALUATE.PORTFOLIO(Portfolio_Context,Portfolio_Book,Portfolio_Pricer,Portfolio_Requests,Portfolio_Currency)</f>
+        <v/>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="22" t="str">
-        <f ca="1">SUBSTITUTE(_xlfn.FORMULATEXT(B82),",",", ")</f>
-        <v>=QS.EVALUATE.PORTFOLIO(Portfolio_Context;Portfolio_Book;Portfolio_Pricer;Portfolio_Requests;Portfolio_Currency)</v>
-      </c>
-      <c r="B83" s="22"/>
-      <c r="C83" s="22"/>
+    <row r="83" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A83" s="13" t="str">
+        <f>SUBSTITUTE(_xlfn.FORMULATEXT(B82),",",", ")</f>
+        <v>=QS.EVALUATE.PORTFOLIO(Portfolio_Context, Portfolio_Book, Portfolio_Pricer, Portfolio_Requests, Portfolio_Currency)</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3397,8 +3270,8 @@
     <mergeCell ref="A83:C83"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="C4" location="'4 Results'!A1" display="Next → 4 Results" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'4 Results'!A1" display="Next → 4 Results"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -3410,221 +3283,221 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF2E7D5B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="70.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="33.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.QS.RESULT.VALUE(Portfolio_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="14" cm="1" t="str">
+        <f t="array" ref="B7">_xll.QS.RESULT.VALUE(Portfolio_Result)</f>
+        <v/>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="33.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="10" t="e">
-        <f ca="1">SUM(B21:B26)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="14">
+        <f>SUM(B21:B26)</f>
+        <v/>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="33.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="10" t="e">
-        <f ca="1">Portfolio_PV-Portfolio_SumPV</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="14">
+        <f>Portfolio_PV-Portfolio_SumPV</f>
+        <v/>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="33.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="15">
         <f>SUMPRODUCT('1 Positions'!C17:C18,'1 Positions'!D17:D18)/SUM('1 Positions'!C17:C18)</f>
-        <v>5.5E-2</v>
-      </c>
-      <c r="C11" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="33.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="15">
         <f>SUMPRODUCT('1 Positions'!C19:C20,'1 Positions'!E19:E20)/SUM('1 Positions'!C19:C20)</f>
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="C12" s="5" t="s">
+        <v/>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:3" ht="24" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-    </row>
-    <row r="16" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-    </row>
-    <row r="17" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-    </row>
-    <row r="20" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:3" ht="24" customHeight="1">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:3" ht="24" customHeight="1">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+    </row>
+    <row r="20" spans="1:3" ht="36" customHeight="1">
+      <c r="A20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="24" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.QS.RESULT.VALUE(Portfolio_C01_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C21" s="7" t="e">
-        <f ca="1">Portfolio_C01_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" cm="1" t="str">
+        <f t="array" ref="B21">_xll.QS.RESULT.VALUE(Portfolio_C01_Result)</f>
+        <v/>
+      </c>
+      <c r="C21" s="10">
+        <f>Portfolio_C01_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="24" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.QS.RESULT.VALUE(Portfolio_C02_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C22" s="7" t="e">
-        <f ca="1">Portfolio_C02_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="14" cm="1" t="str">
+        <f t="array" ref="B22">_xll.QS.RESULT.VALUE(Portfolio_C02_Result)</f>
+        <v/>
+      </c>
+      <c r="C22" s="10">
+        <f>Portfolio_C02_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="24" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.QS.RESULT.VALUE(Portfolio_C03_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" s="7" t="e">
-        <f ca="1">Portfolio_C03_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="14" cm="1" t="str">
+        <f t="array" ref="B23">_xll.QS.RESULT.VALUE(Portfolio_C03_Result)</f>
+        <v/>
+      </c>
+      <c r="C23" s="10">
+        <f>Portfolio_C03_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="24" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.QS.RESULT.VALUE(Portfolio_C04_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C24" s="7" t="e">
-        <f ca="1">Portfolio_C04_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" cm="1" t="str">
+        <f t="array" ref="B24">_xll.QS.RESULT.VALUE(Portfolio_C04_Result)</f>
+        <v/>
+      </c>
+      <c r="C24" s="10">
+        <f>Portfolio_C04_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="24" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.QS.RESULT.VALUE(Portfolio_C05_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C25" s="7" t="e">
-        <f ca="1">Portfolio_C05_Result</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="14" cm="1" t="str">
+        <f t="array" ref="B25">_xll.QS.RESULT.VALUE(Portfolio_C05_Result)</f>
+        <v/>
+      </c>
+      <c r="C25" s="10">
+        <f>Portfolio_C05_Result</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="24" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="10" t="e" cm="1">
-        <f t="array" aca="1" ref="B26" ca="1">_xll.QS.RESULT.VALUE(Portfolio_C06_Result)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C26" s="7" t="e">
-        <f ca="1">Portfolio_C06_Result</f>
-        <v>#VALUE!</v>
+      <c r="B26" s="14" cm="1" t="str">
+        <f t="array" ref="B26">_xll.QS.RESULT.VALUE(Portfolio_C06_Result)</f>
+        <v/>
+      </c>
+      <c r="C26" s="10">
+        <f>Portfolio_C06_Result</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3634,8 +3507,8 @@
     <mergeCell ref="A15:C17"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="C4" location="'5 Coupons'!A1" display="Next → 5 Coupons" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="C4" location="'5 Coupons'!A1" display="Next → 5 Coupons"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -3647,22 +3520,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="14" customWidth="1"/>
     <col min="5" max="6" width="17.7109375" style="1" customWidth="1"/>
     <col min="7" max="8" width="19.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="10" customWidth="1"/>
-    <col min="10" max="12" width="17.7109375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" style="14" customWidth="1"/>
+    <col min="10" max="12" width="17.7109375" style="15" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.7109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="20.7109375" style="1" customWidth="1"/>
@@ -3671,82 +3544,82 @@
     <col min="18" max="18" width="36.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:18" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-    </row>
-    <row r="4" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:18" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">_xll.QS.RESULT.COUPONS(Portfolio_Result)</f>
-        <v>#VALUE!</v>
+    <row r="7" spans="1:18" ht="24" customHeight="1">
+      <c r="A7" s="1" cm="1" t="str">
+        <f t="array" ref="A7">_xll.QS.RESULT.COUPONS(Portfolio_Result)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3755,8 +3628,8 @@
     <mergeCell ref="A2:R3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="R4" location="'6 Cashflows'!A1" display="Next → 6 Cashflows" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="R4" location="'6 Cashflows'!A1" display="Next → 6 Cashflows"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -3767,59 +3640,59 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
-    <col min="3" max="6" width="22.7109375" style="10" customWidth="1"/>
+    <col min="3" max="6" width="22.7109375" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-    </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-    </row>
-    <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">_xll.QS.RESULT.CASHFLOW.SUMMARY(Portfolio_Result)</f>
-        <v>#VALUE!</v>
+    <row r="7" spans="1:6" ht="24" customHeight="1">
+      <c r="A7" s="1" cm="1" t="str">
+        <f t="array" ref="A7">_xll.QS.RESULT.CASHFLOW.SUMMARY(Portfolio_Result)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3828,8 +3701,8 @@
     <mergeCell ref="A2:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="F4" location="'7 Risk'!A1" display="Next → 7 Risk" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
+    <hyperlink ref="F4" location="'7 Risk'!A1" display="Next → 7 Risk"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
@@ -3840,47 +3713,47 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF78909C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="65.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" style="14" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:3" ht="38.25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" ht="24" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">_xll.QS.RESULT.SENSITIVITIES(Portfolio_Result)</f>
-        <v>#VALUE!</v>
+    <row r="7" spans="1:3" ht="24" customHeight="1">
+      <c r="A7" s="1" cm="1" t="str">
+        <f t="array" ref="A7">_xll.QS.RESULT.SENSITIVITIES(Portfolio_Result)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3889,7 +3762,7 @@
     <mergeCell ref="A2:C3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="A4" location="'Start Here'!A1" display="← Start Here"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
